--- a/data/trans_bre/P57_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P57_R-Edad-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 4,39</t>
+          <t>-2,61; 4,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 8,57</t>
+          <t>-0,36; 8,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-36,04; 103,88</t>
+          <t>-35,72; 105,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-37,74; 539,58</t>
+          <t>-24,8; 608,4</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 1,84</t>
+          <t>-5,59; 2,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 1,61</t>
+          <t>-6,87; 1,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,62; 15,99</t>
+          <t>-36,88; 19,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-63,8; 29,53</t>
+          <t>-64,98; 31,88</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 3,4</t>
+          <t>-4,02; 3,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 2,09</t>
+          <t>-4,0; 2,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,53; 26,82</t>
+          <t>-25,02; 25,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-37,9; 33,15</t>
+          <t>-39,48; 34,39</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 5,08</t>
+          <t>-4,84; 5,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 12,65</t>
+          <t>2,7; 11,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 25,16</t>
+          <t>-19,97; 26,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,0; 345,25</t>
+          <t>24,29; 305,65</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,65; 20,11</t>
+          <t>7,97; 20,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 8,1</t>
+          <t>-0,24; 8,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,36; 117,77</t>
+          <t>34,61; 122,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 42,41</t>
+          <t>-1,43; 46,03</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,63; 17,3</t>
+          <t>3,91; 17,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 7,51</t>
+          <t>-13,73; 7,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,67; 74,17</t>
+          <t>12,75; 75,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-62,78; 41,86</t>
+          <t>-66,43; 41,95</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 16,43</t>
+          <t>0,98; 16,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 8,66</t>
+          <t>-1,78; 9,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 45,03</t>
+          <t>2,23; 47,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 31,62</t>
+          <t>-5,07; 34,93</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,96</t>
+          <t>2,9; 6,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 6,42</t>
+          <t>0,23; 6,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,74; 39,33</t>
+          <t>15,13; 40,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,75; 63,47</t>
+          <t>3,27; 61,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P57_R-Edad-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,71</t>
+          <t>4,12</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114,92%</t>
+          <t>120,87%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 4,42</t>
+          <t>-2,54; 4,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 8,76</t>
+          <t>-0,29; 9,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-35,72; 105,37</t>
+          <t>-35,98; 101,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,8; 608,4</t>
+          <t>-15,73; 501,45</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-2,1</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-26,51%</t>
+          <t>-12,92%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 2,0</t>
+          <t>-5,73; 1,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 1,88</t>
+          <t>-5,32; 2,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-36,88; 19,05</t>
+          <t>-37,99; 16,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-64,98; 31,88</t>
+          <t>-49,51; 50,67</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-0,62</t>
+          <t>-1,01</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-7,72%</t>
+          <t>-11,87%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 3,16</t>
+          <t>-4,58; 3,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 2,18</t>
+          <t>-4,43; 1,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 25,16</t>
+          <t>-27,78; 28,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-39,48; 34,39</t>
+          <t>-41,79; 20,38</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,85</t>
+          <t>4,97</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>46,96%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 5,18</t>
+          <t>-4,39; 5,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 11,87</t>
+          <t>1,69; 8,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 26,61</t>
+          <t>-18,03; 28,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,29; 305,65</t>
+          <t>12,22; 90,27</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,88</t>
+          <t>4,57</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,97; 20,35</t>
+          <t>8,61; 19,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 8,87</t>
+          <t>0,24; 8,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,61; 122,75</t>
+          <t>36,04; 113,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 46,03</t>
+          <t>0,88; 45,66</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-2,19</t>
+          <t>6,72</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-11,68%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,91; 17,9</t>
+          <t>3,03; 17,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 7,56</t>
+          <t>2,71; 10,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,75; 75,89</t>
+          <t>10,48; 73,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-66,43; 41,95</t>
+          <t>12,19; 67,63</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,49</t>
+          <t>4,06</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 16,97</t>
+          <t>-0,75; 15,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 9,57</t>
+          <t>-1,45; 9,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 47,53</t>
+          <t>-1,44; 43,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 34,93</t>
+          <t>-4,64; 34,7</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>3,89</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,99</t>
+          <t>2,83; 6,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,23; 6,25</t>
+          <t>2,31; 5,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,13; 40,28</t>
+          <t>14,91; 40,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,27; 61,0</t>
+          <t>15,92; 41,97</t>
         </is>
       </c>
     </row>
